--- a/data/fmsForecastOutput/File1/RPT_RPT8077949212208QB_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT8077949212208QB_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>1035.876388331628</v>
+        <v>427.3018744792801</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>1379.288248395934</v>
+        <v>456.7388515572068</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>2559.305943352527</v>
+        <v>487.8424525677577</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>4157.434861254802</v>
+        <v>547.2716069462224</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>5257.632765576153</v>
+        <v>578.7824836845185</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>1035.876388331628</v>
+        <v>427.3018744792801</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>1379.288248395934</v>
+        <v>456.7388515572068</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>2559.305943352527</v>
+        <v>487.8424525677577</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>4157.434861254802</v>
+        <v>547.2716069462224</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>5257.632765576153</v>
+        <v>578.7824836845185</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>14328868.13562215</v>
+        <v>5910697.726568529</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>21063897.75352982</v>
+        <v>6975119.581026077</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>42672117.70450221</v>
+        <v>8133951.554832515</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>70941074.7983125</v>
+        <v>9338459.242064159</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>98340968.6648657</v>
+        <v>10825790.35653797</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>1033.227911143255</v>
+        <v>426.2093703157957</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>1375.761752857262</v>
+        <v>455.5710843959712</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>2552.762437307415</v>
+        <v>486.5951612676571</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>4146.805338740139</v>
+        <v>545.8723701423256</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>5244.190311822673</v>
+        <v>577.3026814394483</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>1033.227911143255</v>
+        <v>426.2093703157957</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>1375.761752857262</v>
+        <v>455.5710843959712</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>2552.762437307415</v>
+        <v>486.5951612676571</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>4146.805338740139</v>
+        <v>545.8723701423256</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>5244.190311822673</v>
+        <v>577.3026814394483</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>14328868.13562215</v>
+        <v>5910697.726568529</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>21063897.75352982</v>
+        <v>6975119.581026077</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>42672117.70450221</v>
+        <v>8133951.554832515</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>70941074.7983125</v>
+        <v>9338459.242064159</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>98340968.6648657</v>
+        <v>10825790.35653797</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>-2203.722707482101</v>
+        <v>-880.6491474337354</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>-3010.655933327753</v>
+        <v>-961.1622192276441</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>-5539.942822160543</v>
+        <v>-1033.809756857378</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>-10247.94747891801</v>
+        <v>-1306.577477088223</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>-12916.89593083025</v>
+        <v>-1386.477084760488</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>-2203.722707482101</v>
+        <v>-880.6491474337353</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>-3010.655933327753</v>
+        <v>-961.1622192276441</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>-5539.942822160543</v>
+        <v>-1033.809756857378</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>-10247.94747891801</v>
+        <v>-1306.577477088223</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>-12916.89593083025</v>
+        <v>-1386.477084760488</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>5939097.68290917</v>
+        <v>2373375.42206277</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>8719572.547900653</v>
+        <v>2783753.403396368</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>17279893.10797703</v>
+        <v>3224604.055662848</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>28233791.88851885</v>
+        <v>3599709.761415538</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>39130561.7439777</v>
+        <v>4200206.261810708</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>-2723.992506923595</v>
+        <v>-1088.558769528235</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>-3721.432000253811</v>
+        <v>-1188.079913241726</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>-6847.850087996172</v>
+        <v>-1277.878574152176</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>-12667.3524074244</v>
+        <v>-1615.04314731592</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>-15966.40430705333</v>
+        <v>-1713.805996138248</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>-2723.992506923595</v>
+        <v>-1088.558769528235</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>-3721.432000253811</v>
+        <v>-1188.079913241726</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>-6847.850087996172</v>
+        <v>-1277.878574152176</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>-12667.3524074244</v>
+        <v>-1615.04314731592</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>-15966.40430705333</v>
+        <v>-1713.805996138248</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>5939097.68290917</v>
+        <v>2373375.42206277</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>8719572.547900653</v>
+        <v>2783753.403396368</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>17279893.10797703</v>
+        <v>3224604.055662848</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>28233791.88851885</v>
+        <v>3599709.761415538</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>39130561.7439777</v>
+        <v>4200206.261810708</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>1819.782694809051</v>
+        <v>743.79506524666</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>2406.680175848501</v>
+        <v>788.5745318639019</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>4423.14145555089</v>
+        <v>838.0118950990116</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>6931.138535537294</v>
+        <v>904.2234666418735</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>8770.107766494048</v>
+        <v>958.5956397661212</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>1819.782694809051</v>
+        <v>743.79506524666</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>2406.680175848501</v>
+        <v>788.5745318639019</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>4423.14145555089</v>
+        <v>838.0118950990116</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>6931.138535537294</v>
+        <v>904.2234666418735</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>8770.107766494048</v>
+        <v>958.5956397661212</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>20267965.81853132</v>
+        <v>8284073.148631302</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>29783470.30143048</v>
+        <v>9758872.984422443</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>59952010.81247923</v>
+        <v>11358555.61049536</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>99174866.68683134</v>
+        <v>12938169.0034797</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>137471530.4088434</v>
+        <v>15025996.61834868</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>1734.117452313387</v>
+        <v>708.7813326657376</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>2296.752079481412</v>
+        <v>752.5554139099328</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>4224.158731583957</v>
+        <v>800.3124700909721</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>6665.631069366969</v>
+        <v>869.5858554833453</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>8433.029941027757</v>
+        <v>921.7521547877142</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>1734.117452313387</v>
+        <v>708.7813326657376</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>2296.752079481412</v>
+        <v>752.5554139099328</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>4224.158731583957</v>
+        <v>800.3124700909721</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>6665.631069366969</v>
+        <v>869.5858554833453</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>8433.029941027757</v>
+        <v>921.7521547877142</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>20267965.81853132</v>
+        <v>8284073.148631302</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>29783470.30143048</v>
+        <v>9758872.984422443</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>59952010.81247923</v>
+        <v>11358555.61049536</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>99174866.68683134</v>
+        <v>12938169.0034797</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>137471530.4088434</v>
+        <v>15025996.61834868</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1634.94542286805</v>
+        <v>1124.806870658283</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>2028.34979352943</v>
+        <v>1227.035498543696</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>5371.991993830822</v>
+        <v>1304.338386192193</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>9304.37311585922</v>
+        <v>1406.393365540603</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>12233.28040170772</v>
+        <v>1482.216069668771</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>1634.94542286805</v>
+        <v>1124.806870658283</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>2028.34979352943</v>
+        <v>1227.035498543696</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>5371.991993830822</v>
+        <v>1304.338386192193</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>9304.37311585922</v>
+        <v>1406.393365540603</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>12233.28040170772</v>
+        <v>1482.216069668771</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>129532.9414513425</v>
+        <v>89115.844775698</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>176832.6795069834</v>
+        <v>106973.6471243024</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>529048.3668974102</v>
+        <v>128454.7880728496</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>1009410.57655219</v>
+        <v>152576.462733397</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>1522211.112573159</v>
+        <v>184435.0573513667</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1678.013754576323</v>
+        <v>1154.436945604928</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>2081.781327393654</v>
+        <v>1259.35851748362</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>5513.502976331163</v>
+        <v>1338.697746138175</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>9549.472323506414</v>
+        <v>1443.441095166441</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>12555.53395883064</v>
+        <v>1521.261148763731</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1678.013754576323</v>
+        <v>1154.436945604928</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>2081.781327393654</v>
+        <v>1259.35851748362</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>5513.502976331163</v>
+        <v>1338.697746138175</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>9549.472323506414</v>
+        <v>1443.441095166441</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>12555.53395883064</v>
+        <v>1521.261148763731</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>129532.9414513425</v>
+        <v>89115.844775698</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>176832.6795069834</v>
+        <v>106973.6471243024</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>529048.3668974102</v>
+        <v>128454.7880728496</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>1009410.57655219</v>
+        <v>152576.462733397</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>1522211.112573159</v>
+        <v>184435.0573513667</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>1818.477132971864</v>
+        <v>746.4862674454344</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>2404.033594629946</v>
+        <v>791.6417519808041</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>4429.985940761616</v>
+        <v>841.3757175798869</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>6948.996993476185</v>
+        <v>908.0022671414193</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>8797.382740164619</v>
+        <v>962.7195270057437</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>1818.477132971864</v>
+        <v>746.4862674454344</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>2404.033594629946</v>
+        <v>791.6417519808041</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>4429.985940761616</v>
+        <v>841.3757175798869</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>6948.996993476185</v>
+        <v>908.0022671414193</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>8797.382740164619</v>
+        <v>962.7195270057437</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>20397498.75998267</v>
+        <v>8373188.993406999</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>29960302.98093746</v>
+        <v>9865846.631546745</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>60481059.17937665</v>
+        <v>11487010.39856821</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>100184277.2633835</v>
+        <v>13090745.46621309</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>138993741.5214165</v>
+        <v>15210431.67570004</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>1733.749335554487</v>
+        <v>711.7054411726247</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>2295.353104015524</v>
+        <v>755.8535607557238</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>4232.817313850068</v>
+        <v>803.9279926502173</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>6685.974536684858</v>
+        <v>873.6339997065879</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>8463.463565109976</v>
+        <v>926.1779191478662</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>1733.749335554487</v>
+        <v>711.7054411726247</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>2295.353104015524</v>
+        <v>755.8535607557238</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>4232.817313850068</v>
+        <v>803.9279926502173</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>6685.974536684858</v>
+        <v>873.6339997065879</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>8463.463565109976</v>
+        <v>926.1779191478662</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>20397498.75998267</v>
+        <v>8373188.993406999</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>29960302.98093746</v>
+        <v>9865846.631546745</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>60481059.17937665</v>
+        <v>11487010.39856821</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>100184277.2633835</v>
+        <v>13090745.46621309</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>138993741.5214165</v>
+        <v>15210431.67570004</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>2419.715447419712</v>
+        <v>2405.772634899196</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>2510.876375490593</v>
+        <v>2482.31716690983</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>9814.314073183194</v>
+        <v>2599.171141706202</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>16687.83714716609</v>
+        <v>2715.850862337903</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>24153.40702727433</v>
+        <v>2868.612004482441</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2419.715447419712</v>
+        <v>2405.772634899196</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2510.876375490593</v>
+        <v>2482.31716690983</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>9814.314073183194</v>
+        <v>2599.171141706202</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>16687.83714716609</v>
+        <v>2715.850862337903</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>24153.40702727433</v>
+        <v>2868.612004482441</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>3088034.62401939</v>
+        <v>3070240.8425789</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>3639964.492773952</v>
+        <v>3598562.81079931</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>16005041.33123478</v>
+        <v>4238690.675655939</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>30709634.86031796</v>
+        <v>4997818.925362656</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>50461262.37680035</v>
+        <v>5993099.973513875</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>1286.787365461329</v>
+        <v>1279.37267750307</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>1335.266094888141</v>
+        <v>1320.078512063686</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>5219.182017252664</v>
+        <v>1382.220619943459</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>8874.472418130095</v>
+        <v>1444.27006070499</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>12844.60907528787</v>
+        <v>1525.507343317972</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>1286.787365461329</v>
+        <v>1279.37267750307</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>1335.266094888141</v>
+        <v>1320.078512063686</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>5219.182017252664</v>
+        <v>1382.220619943459</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>8874.472418130095</v>
+        <v>1444.27006070499</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>12844.60907528787</v>
+        <v>1525.507343317972</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>3088034.62401939</v>
+        <v>3070240.8425789</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>3639964.492773952</v>
+        <v>3598562.81079931</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>16005041.33123478</v>
+        <v>4238690.675655939</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>30709634.86031796</v>
+        <v>4997818.925362656</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>50461262.37680035</v>
+        <v>5993099.973513875</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>1879.895430944875</v>
+        <v>915.9873489465674</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>2415.166830258134</v>
+        <v>967.8135776630661</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>5004.508786726577</v>
+        <v>1028.93739748795</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>8051.380600180783</v>
+        <v>1112.640871256247</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>10590.79921715055</v>
+        <v>1185.307021565742</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>1879.895430944875</v>
+        <v>915.9873489465674</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>2415.166830258134</v>
+        <v>967.8135776630661</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>5004.508786726577</v>
+        <v>1028.93739748795</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>8051.380600180783</v>
+        <v>1112.640871256247</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>10590.79921715055</v>
+        <v>1185.307021565742</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>23485533.38400206</v>
+        <v>11443429.8359859</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>33600267.47371142</v>
+        <v>13464409.44234606</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>76486100.51061144</v>
+        <v>15725701.07422415</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>130893912.1237015</v>
+        <v>18088564.39157575</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>189455003.8982169</v>
+        <v>21203531.64921392</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>1658.024813065677</v>
+        <v>807.8799107694582</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>2129.481850267815</v>
+        <v>853.3329549975583</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>4407.103351027373</v>
+        <v>906.1095995062898</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>7096.563111819394</v>
+        <v>980.6922012210409</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>9309.191726019255</v>
+        <v>1041.871353776934</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>1658.024813065677</v>
+        <v>807.8799107694582</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>2129.481850267815</v>
+        <v>853.3329549975583</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>4407.103351027373</v>
+        <v>906.1095995062898</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>7096.563111819394</v>
+        <v>980.6922012210409</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>9309.191726019255</v>
+        <v>1041.871353776934</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>23485533.38400206</v>
+        <v>11443429.8359859</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>33600267.47371142</v>
+        <v>13464409.44234606</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>76486100.51061144</v>
+        <v>15725701.07422415</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>130893912.1237015</v>
+        <v>18088564.39157575</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>189455003.8982169</v>
+        <v>21203531.64921392</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3289,19 +3289,19 @@
         </is>
       </c>
       <c r="C20" s="79" t="n">
-        <v>-2695.029489302209</v>
+        <v>-2695.029489302215</v>
       </c>
       <c r="D20" s="80" t="n">
-        <v>-2896.236813837008</v>
+        <v>-2896.236813836996</v>
       </c>
       <c r="E20" s="80" t="n">
-        <v>-3119.146471847156</v>
+        <v>-3119.146471847148</v>
       </c>
       <c r="F20" s="80" t="n">
-        <v>-2755.067973035689</v>
+        <v>-2755.067973035692</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>-3029.40907424827</v>
+        <v>-3029.409074248268</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>0</v>
@@ -3319,19 +3319,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="79" t="n">
-        <v>-2695.029489302209</v>
+        <v>-2695.029489302215</v>
       </c>
       <c r="N20" s="80" t="n">
-        <v>-2896.236813837008</v>
+        <v>-2896.236813836996</v>
       </c>
       <c r="O20" s="80" t="n">
-        <v>-3119.146471847156</v>
+        <v>-3119.146471847148</v>
       </c>
       <c r="P20" s="80" t="n">
-        <v>-2755.067973035689</v>
+        <v>-2755.067973035692</v>
       </c>
       <c r="Q20" s="81" t="n">
-        <v>-3029.40907424827</v>
+        <v>-3029.409074248268</v>
       </c>
       <c r="S20" s="32" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="T20" s="79" t="n">
-        <v>-2180.291490455174</v>
+        <v>-2180.291490455178</v>
       </c>
       <c r="U20" s="80" t="n">
-        <v>-2343.069159212356</v>
+        <v>-2343.069159212347</v>
       </c>
       <c r="V20" s="80" t="n">
-        <v>-2523.404117486091</v>
+        <v>-2523.404117486085</v>
       </c>
       <c r="W20" s="80" t="n">
-        <v>-2228.862905240631</v>
+        <v>-2228.862905240634</v>
       </c>
       <c r="X20" s="81" t="n">
-        <v>-2450.8061421626</v>
+        <v>-2450.806142162598</v>
       </c>
       <c r="Y20" s="79" t="n">
         <v>0</v>
@@ -3369,19 +3369,19 @@
         <v>0</v>
       </c>
       <c r="AD20" s="79" t="n">
-        <v>-2180.291490455174</v>
+        <v>-2180.291490455178</v>
       </c>
       <c r="AE20" s="80" t="n">
-        <v>-2343.069159212356</v>
+        <v>-2343.069159212347</v>
       </c>
       <c r="AF20" s="80" t="n">
-        <v>-2523.404117486091</v>
+        <v>-2523.404117486085</v>
       </c>
       <c r="AG20" s="80" t="n">
-        <v>-2228.862905240631</v>
+        <v>-2228.862905240634</v>
       </c>
       <c r="AH20" s="81" t="n">
-        <v>-2450.8061421626</v>
+        <v>-2450.806142162598</v>
       </c>
       <c r="AS20" s="82" t="inlineStr">
         <is>
@@ -3409,13 +3409,13 @@
         </is>
       </c>
       <c r="C21" s="85" t="n">
-        <v>11137.57476447375</v>
+        <v>11137.57476447374</v>
       </c>
       <c r="D21" s="86" t="n">
-        <v>12375.33370670243</v>
+        <v>12375.33370670244</v>
       </c>
       <c r="E21" s="86" t="n">
-        <v>13554.16990728197</v>
+        <v>13554.16990728198</v>
       </c>
       <c r="F21" s="86" t="n">
         <v>14308.59680243621</v>
@@ -3439,13 +3439,13 @@
         <v>0</v>
       </c>
       <c r="M21" s="85" t="n">
-        <v>11137.57476447375</v>
+        <v>11137.57476447374</v>
       </c>
       <c r="N21" s="86" t="n">
-        <v>12375.33370670243</v>
+        <v>12375.33370670244</v>
       </c>
       <c r="O21" s="86" t="n">
-        <v>13554.16990728197</v>
+        <v>13554.16990728198</v>
       </c>
       <c r="P21" s="86" t="n">
         <v>14308.59680243621</v>
@@ -3462,10 +3462,10 @@
         <v>11687.7699324766</v>
       </c>
       <c r="U21" s="86" t="n">
-        <v>12967.64703840187</v>
+        <v>12967.64703840188</v>
       </c>
       <c r="V21" s="86" t="n">
-        <v>14192.65103941742</v>
+        <v>14192.65103941743</v>
       </c>
       <c r="W21" s="86" t="n">
         <v>14878.54122959282</v>
@@ -3492,10 +3492,10 @@
         <v>11687.7699324766</v>
       </c>
       <c r="AE21" s="86" t="n">
-        <v>12967.64703840187</v>
+        <v>12967.64703840188</v>
       </c>
       <c r="AF21" s="86" t="n">
-        <v>14192.65103941742</v>
+        <v>14192.65103941743</v>
       </c>
       <c r="AG21" s="86" t="n">
         <v>14878.54122959282</v>
@@ -3706,10 +3706,10 @@
         <v>11216.80244977722</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>12462.51427095771</v>
+        <v>12462.51427095772</v>
       </c>
       <c r="E23" s="86" t="n">
-        <v>13652.65262421546</v>
+        <v>13652.65262421547</v>
       </c>
       <c r="F23" s="86" t="n">
         <v>14417.08456018011</v>
@@ -3736,10 +3736,10 @@
         <v>11216.80244977722</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>12462.51427095771</v>
+        <v>12462.51427095772</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>13652.65262421546</v>
+        <v>13652.65262421547</v>
       </c>
       <c r="P23" s="86" t="n">
         <v>14417.08456018011</v>
@@ -3756,7 +3756,7 @@
         <v>11764.96413967429</v>
       </c>
       <c r="U23" s="86" t="n">
-        <v>13052.59000391899</v>
+        <v>13052.590003919</v>
       </c>
       <c r="V23" s="86" t="n">
         <v>14288.60607366127</v>
@@ -3786,7 +3786,7 @@
         <v>11764.96413967429</v>
       </c>
       <c r="AE23" s="86" t="n">
-        <v>13052.59000391899</v>
+        <v>13052.590003919</v>
       </c>
       <c r="AF23" s="86" t="n">
         <v>14288.60607366127</v>
@@ -3945,7 +3945,7 @@
         <v>12492.99987510355</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>13912.1931672605</v>
+        <v>13912.19316726051</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>15283.4381495093</v>
@@ -3975,7 +3975,7 @@
         <v>12492.99987510355</v>
       </c>
       <c r="N25" s="92" t="n">
-        <v>13912.1931672605</v>
+        <v>13912.19316726051</v>
       </c>
       <c r="O25" s="92" t="n">
         <v>15283.4381495093</v>
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>14164.76593047933</v>
+        <v>14164.76593047932</v>
       </c>
       <c r="U25" s="92" t="n">
         <v>15778.6118108899</v>
       </c>
       <c r="V25" s="92" t="n">
-        <v>17355.18648383438</v>
+        <v>17355.18648383439</v>
       </c>
       <c r="W25" s="92" t="n">
         <v>18444.69076949325</v>
@@ -4022,13 +4022,13 @@
         <v>0</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>14164.76593047933</v>
+        <v>14164.76593047932</v>
       </c>
       <c r="AE25" s="92" t="n">
         <v>15778.6118108899</v>
       </c>
       <c r="AF25" s="92" t="n">
-        <v>17355.18648383438</v>
+        <v>17355.18648383439</v>
       </c>
       <c r="AG25" s="92" t="n">
         <v>18444.69076949325</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>1069.122999816242</v>
+        <v>437.4327648098953</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>1459.892458686141</v>
+        <v>478.3643299381642</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>2735.140011446306</v>
+        <v>514.1032757729005</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>4484.877666315718</v>
+        <v>586.240380959759</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>5686.863733551212</v>
+        <v>621.7010533425051</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>1069.122999816242</v>
+        <v>437.4327648098953</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>1459.892458686141</v>
+        <v>478.3643299381642</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>2735.140011446306</v>
+        <v>514.1032757729005</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>4484.877666315718</v>
+        <v>586.240380959759</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>5686.863733551212</v>
+        <v>621.7010533425051</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>14788755.35506787</v>
+        <v>6050834.323250336</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>22294850.6352291</v>
+        <v>7305374.599161268</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>45603854.75205911</v>
+        <v>8571806.568508238</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>76528449.05701214</v>
+        <v>10003409.33854227</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>106369484.7392476</v>
+        <v>11628557.28645959</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>1066.389519346494</v>
+        <v>436.3143584902842</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>1456.159878314717</v>
+        <v>477.1412718302242</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>2728.146941608129</v>
+        <v>512.7888421071758</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>4473.410954335719</v>
+        <v>584.7415107341563</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>5672.323843424018</v>
+        <v>620.1115190348287</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>1066.389519346494</v>
+        <v>436.3143584902842</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>1456.159878314717</v>
+        <v>477.1412718302242</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>2728.146941608129</v>
+        <v>512.7888421071758</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>4473.410954335719</v>
+        <v>584.7415107341563</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>5672.323843424018</v>
+        <v>620.1115190348287</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>14788755.35506787</v>
+        <v>6050834.323250336</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>22294850.6352291</v>
+        <v>7305374.599161268</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>45603854.75205911</v>
+        <v>8571806.568508238</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>76528449.05701214</v>
+        <v>10003409.33854227</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>106369484.7392476</v>
+        <v>11628557.28645959</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>-2279.180788548029</v>
+        <v>-896.1071619080554</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>-3200.702798246351</v>
+        <v>-999.0817643778397</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>-5969.929626946207</v>
+        <v>-1079.887301221941</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>-11051.71767969621</v>
+        <v>-1399.789487210977</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>-13970.88572896379</v>
+        <v>-1489.170147865981</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>-2279.180788548029</v>
+        <v>-896.1071619080553</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>-3200.702798246351</v>
+        <v>-999.0817643778397</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>-5969.929626946207</v>
+        <v>-1079.887301221941</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>-11051.71767969621</v>
+        <v>-1399.789487210977</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>-13970.88572896379</v>
+        <v>-1489.170147865981</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>6142459.436588002</v>
+        <v>2415035.226917123</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>9269993.274432207</v>
+        <v>2893577.386024319</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>18621084.93306507</v>
+        <v>3368326.665598955</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>30448233.42636333</v>
+        <v>3856515.185207017</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>42323528.00260857</v>
+        <v>4511305.559044838</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>-2817.26524342195</v>
+        <v>-1107.666216874946</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>-3956.346417682523</v>
+        <v>-1234.951761729915</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>-7379.351093243076</v>
+        <v>-1334.834417625749</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>-13660.88212728189</v>
+        <v>-1730.26128082591</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>-17269.22716345983</v>
+        <v>-1840.743533906786</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>-2817.26524342195</v>
+        <v>-1107.666216874946</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>-3956.346417682523</v>
+        <v>-1234.951761729915</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>-7379.351093243076</v>
+        <v>-1334.834417625749</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>-13660.88212728189</v>
+        <v>-1730.26128082591</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>-17269.22716345983</v>
+        <v>-1840.743533906786</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>6142459.436588002</v>
+        <v>2415035.226917123</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>9269993.274432207</v>
+        <v>2893577.386024319</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>18621084.93306507</v>
+        <v>3368326.665598955</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>30448233.42636333</v>
+        <v>3856515.185207017</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>42323528.00260857</v>
+        <v>4511305.559044838</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>1879.333269072324</v>
+        <v>760.1178649028334</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>2550.625676668898</v>
+        <v>824.1355123750616</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>4738.389744592133</v>
+        <v>880.9195484330146</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>7476.392266861653</v>
+        <v>968.6431671196065</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>9485.991332114121</v>
+        <v>1029.65563902969</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>1879.333269072324</v>
+        <v>760.1178649028334</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>2550.625676668898</v>
+        <v>824.1355123750616</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>4738.389744592133</v>
+        <v>880.9195484330146</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>7476.392266861653</v>
+        <v>968.6431671196065</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>9485.991332114121</v>
+        <v>1029.65563902969</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>20931214.79165587</v>
+        <v>8465869.55016746</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>31564843.90966131</v>
+        <v>10198951.98518559</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>64224939.68512417</v>
+        <v>11940133.23410719</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>106976682.4833755</v>
+        <v>13859924.52374928</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>148693012.7418562</v>
+        <v>16139862.84550443</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>1790.86471692899</v>
+        <v>724.3357457476554</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>2434.122691355374</v>
+        <v>786.4921026137439</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>4525.225027146194</v>
+        <v>841.2898478899898</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>7189.998053747578</v>
+        <v>931.5378644905356</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>9121.398625187856</v>
+        <v>990.0809732417486</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>1790.86471692899</v>
+        <v>724.3357457476554</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>2434.122691355374</v>
+        <v>786.4921026137439</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>4525.225027146194</v>
+        <v>841.2898478899898</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>7189.998053747578</v>
+        <v>931.5378644905356</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>9121.398625187856</v>
+        <v>990.0809732417486</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>20931214.79165587</v>
+        <v>8465869.55016746</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>31564843.90966131</v>
+        <v>10198951.98518559</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>64224939.68512417</v>
+        <v>11940133.23410719</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>106976682.4833755</v>
+        <v>13859924.52374928</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>148693012.7418562</v>
+        <v>16139862.84550443</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>1688.66880221123</v>
+        <v>1151.345916698642</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>2156.081076433932</v>
+        <v>1286.332791451269</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>5850.073032139856</v>
+        <v>1376.982236916516</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>10283.07756917226</v>
+        <v>1506.855402789324</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>13637.63556319862</v>
+        <v>1594.151955973489</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>1688.66880221123</v>
+        <v>1151.345916698642</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>2156.081076433932</v>
+        <v>1286.332791451269</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>5850.073032139856</v>
+        <v>1376.982236916516</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>10283.07756917226</v>
+        <v>1506.855402789324</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>13637.63556319862</v>
+        <v>1594.151955973489</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>133789.320443383</v>
+        <v>91218.47196363796</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>187968.3648236491</v>
+        <v>112143.2185787955</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>576131.0864644673</v>
+        <v>135608.9518606918</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>1115588.028186091</v>
+        <v>163475.363892895</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>1696957.784162776</v>
+        <v>198363.4595814818</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1733.152334873418</v>
+        <v>1181.675092925429</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>2212.877354579347</v>
+        <v>1320.217841419646</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>6004.177800618208</v>
+        <v>1413.255207809873</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>10553.95816832652</v>
+        <v>1546.549540230249</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>13996.88315882908</v>
+        <v>1636.145691221739</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1733.152334873418</v>
+        <v>1181.675092925429</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>2212.877354579347</v>
+        <v>1320.217841419646</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>6004.177800618208</v>
+        <v>1413.255207809873</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>10553.95816832652</v>
+        <v>1546.549540230249</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>13996.88315882908</v>
+        <v>1636.145691221739</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>133789.320443383</v>
+        <v>91218.47196363796</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>187968.3648236491</v>
+        <v>112143.2185787955</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>576131.0864644673</v>
+        <v>135608.9518606918</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>1115588.028186091</v>
+        <v>163475.363892895</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>1696957.784162776</v>
+        <v>198363.4595814818</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>1877.986547986109</v>
+        <v>762.8812275552785</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>2547.865670130529</v>
+        <v>827.3687780477054</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>4746.408815577142</v>
+        <v>884.4978714648726</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>7497.512417324074</v>
+        <v>972.6931841944462</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>9518.688514443706</v>
+        <v>1034.101453259458</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>1877.986547986109</v>
+        <v>762.8812275552785</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>2547.865670130529</v>
+        <v>827.3687780477054</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>4746.408815577142</v>
+        <v>884.4978714648726</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>7497.512417324074</v>
+        <v>972.6931841944462</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>9518.688514443706</v>
+        <v>1034.101453259458</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>21065004.11209925</v>
+        <v>8557088.022131098</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>31752812.27448496</v>
+        <v>10311095.20376438</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>64801070.77158865</v>
+        <v>12075742.18596788</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>108092270.5115616</v>
+        <v>14023399.88764218</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>150389970.5260189</v>
+        <v>16338226.30508591</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>1790.486045007395</v>
+        <v>727.3365154828258</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>2432.682882473999</v>
+        <v>789.9654551831095</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>4535.156924162038</v>
+        <v>845.1308772678361</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>7213.728421205006</v>
+        <v>935.8763383602651</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>9157.390988779194</v>
+        <v>994.8504266309697</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>1790.486045007395</v>
+        <v>727.3365154828258</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>2432.682882473999</v>
+        <v>789.9654551831095</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>4535.156924162038</v>
+        <v>845.1308772678361</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>7213.728421205006</v>
+        <v>935.8763383602651</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>9157.390988779194</v>
+        <v>994.8504266309697</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>21065004.11209925</v>
+        <v>8557088.022131098</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>31752812.27448496</v>
+        <v>10311095.20376438</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>64801070.77158865</v>
+        <v>12075742.18596788</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>108092270.5115616</v>
+        <v>14023399.88764218</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>150389970.5260189</v>
+        <v>16338226.30508591</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>2471.555258869131</v>
+        <v>2457.12939159514</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>2620.569672097906</v>
+        <v>2590.291948384115</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>10433.14200902093</v>
+        <v>2724.239361132865</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>18016.50055432259</v>
+        <v>2876.098097708331</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>26197.27754816462</v>
+        <v>3038.608568153732</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2471.555258869131</v>
+        <v>2457.12939159514</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>2620.569672097906</v>
+        <v>2590.291948384115</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>10433.14200902093</v>
+        <v>2724.239361132865</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>18016.50055432259</v>
+        <v>2876.098097708331</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>26197.27754816462</v>
+        <v>3038.608568153732</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>3154192.457920541</v>
+        <v>3135782.203247375</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>3798984.549931457</v>
+        <v>3755091.572835487</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>17014216.97164643</v>
+        <v>4442650.117571215</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>33154695.15939758</v>
+        <v>5292712.388320316</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>54731313.65786351</v>
+        <v>6348256.543884459</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>1314.355406353138</v>
+        <v>1306.683833332522</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>1393.600205331009</v>
+        <v>1377.498728452237</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>5548.270286734786</v>
+        <v>1448.731004356879</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>9581.046113439163</v>
+        <v>1529.488394143602</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>13931.52479743406</v>
+        <v>1615.910299804994</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>1314.355406353138</v>
+        <v>1306.683833332522</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>1393.600205331009</v>
+        <v>1377.498728452237</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>5548.270286734786</v>
+        <v>1448.731004356879</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>9581.046113439163</v>
+        <v>1529.488394143602</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>13931.52479743406</v>
+        <v>1615.910299804994</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>3154192.457920541</v>
+        <v>3135782.203247375</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>3798984.549931457</v>
+        <v>3755091.572835487</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>17014216.97164643</v>
+        <v>4442650.117571215</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>33154695.15939758</v>
+        <v>5292712.388320316</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>54731313.65786351</v>
+        <v>6348256.543884459</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>1938.621372940584</v>
+        <v>935.9537614884956</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>2555.441575385849</v>
+        <v>1011.068967163405</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>5353.199125935018</v>
+        <v>1080.80342537778</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>8688.204522169202</v>
+        <v>1188.148242544868</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>11466.56615690489</v>
+        <v>1268.206063988981</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>1938.621372940584</v>
+        <v>935.9537614884956</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>2555.441575385849</v>
+        <v>1011.068967163405</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>5353.199125935018</v>
+        <v>1080.80342537778</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>8688.204522169202</v>
+        <v>1188.148242544868</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>11466.56615690489</v>
+        <v>1268.206063988981</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>24219196.5700198</v>
+        <v>11692870.22537847</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>35551796.82441641</v>
+        <v>14066186.77659987</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>81815287.74323508</v>
+        <v>16518392.3035391</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>141246965.6709591</v>
+        <v>19316112.27596249</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>205121284.1838825</v>
+        <v>22686482.84897038</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>1709.819751973849</v>
+        <v>825.4898303838612</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>2253.163792259576</v>
+        <v>891.4717558924814</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>4714.169324509568</v>
+        <v>951.7842011623025</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>7657.865747718347</v>
+        <v>1047.245113369455</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>10078.98087812404</v>
+        <v>1114.738666620673</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>1709.819751973849</v>
+        <v>825.4898303838612</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>2253.163792259576</v>
+        <v>891.4717558924814</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>4714.169324509568</v>
+        <v>951.7842011623025</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>7657.865747718347</v>
+        <v>1047.245113369455</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>10078.98087812404</v>
+        <v>1114.738666620673</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>24219196.5700198</v>
+        <v>11692870.22537847</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>35551796.82441641</v>
+        <v>14066186.77659987</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>81815287.74323508</v>
+        <v>16518392.3035391</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>141246965.6709591</v>
+        <v>19316112.27596249</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>205121284.1838825</v>
+        <v>22686482.84897038</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>-0.254325617176621</v>
+        <v>0.2951150481454211</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>-0.3488419925481428</v>
+        <v>0.1834939607823052</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>-0.7451419772107838</v>
+        <v>0.1287310760429539</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>-0.9290565750006341</v>
+        <v>0.0885980167100989</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>-0.6642393709654838</v>
+        <v>0.04738202949377251</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>-0.254325617176621</v>
+        <v>0.2951150481454211</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>-0.3488419925481428</v>
+        <v>0.1834939607823052</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>-0.7451419772107838</v>
+        <v>0.1287310760429539</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>-0.9290565750006341</v>
+        <v>0.0885980167100989</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>-0.6642393709654838</v>
+        <v>0.04738202949377251</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>-3517.985614001524</v>
+        <v>4082.209670329649</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>-5327.365089724455</v>
+        <v>2802.240962180071</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>-12423.98793340522</v>
+        <v>2146.373958689901</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>-15853.10995325889</v>
+        <v>1511.806856912785</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>-12424.21182281423</v>
+        <v>886.2533549762308</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>-0.2536753700978204</v>
+        <v>0.2943605126798357</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>-0.3479500907053966</v>
+        <v>0.1830248125568892</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>-0.7432368352933004</v>
+        <v>0.128401942835387</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>-0.9266812093939713</v>
+        <v>0.08837149371098921</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>-0.662541076804677</v>
+        <v>0.04726088547922925</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>-0.2536753700978204</v>
+        <v>0.2943605126798357</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>-0.3479500907053966</v>
+        <v>0.1830248125568892</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>-0.7432368352933004</v>
+        <v>0.128401942835387</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>-0.9266812093939713</v>
+        <v>0.08837149371098921</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>-0.662541076804677</v>
+        <v>0.04726088547922925</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>-3517.985614001524</v>
+        <v>4082.209670329649</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>-5327.365089724455</v>
+        <v>2802.240962180071</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>-12423.98793340522</v>
+        <v>2146.373958689901</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>-15853.10995325889</v>
+        <v>1511.806856912785</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>-12424.21182281423</v>
+        <v>886.2533549762308</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.2786467962963702</v>
+        <v>-0.3162910655220251</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.2710627640244656</v>
+        <v>-0.1418292540798702</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.5585201901333249</v>
+        <v>-0.1018383161844659</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>0.8410745562131094</v>
+        <v>-0.08040795851929951</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.5900528323002023</v>
+        <v>-0.0426256615049324</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.2786467962963702</v>
+        <v>-0.3162910655220251</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.2710627640244656</v>
+        <v>-0.1418292540798702</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>0.5585201901333249</v>
+        <v>-0.1018383161844659</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>0.8410745562131094</v>
+        <v>-0.08040795851929951</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.5900528323002023</v>
+        <v>-0.0426256615049324</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>-750.9613331183034</v>
+        <v>852.4137487846765</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>-785.0619560280709</v>
+        <v>410.7711069451609</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>-1742.106280509763</v>
+        <v>317.6486246256312</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>-2317.217572757943</v>
+        <v>221.5293912937045</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>-1787.511404456126</v>
+        <v>129.1305657588773</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3444316213707402</v>
+        <v>-0.3909632049275754</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.3350570993354616</v>
+        <v>-0.1753132660767243</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.6903794237465674</v>
+        <v>-0.1258809963986606</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>1.03964114047103</v>
+        <v>-0.09939121458427594</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.7293565058878215</v>
+        <v>-0.05268901670245208</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.3444316213707402</v>
+        <v>-0.3909632049275754</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.3350570993354616</v>
+        <v>-0.1753132660767243</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.6903794237465674</v>
+        <v>-0.1258809963986606</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>1.03964114047103</v>
+        <v>-0.09939121458427594</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.7293565058878215</v>
+        <v>-0.05268901670245208</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>-750.9613331183034</v>
+        <v>852.4137487846765</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>-785.0619560280709</v>
+        <v>410.7711069451609</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>-1742.106280509763</v>
+        <v>317.6486246256312</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>-2317.217572757943</v>
+        <v>221.5293912937045</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>-1787.511404456126</v>
+        <v>129.1305657588773</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>-0.3832923268660576</v>
+        <v>0.4430608569160513</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>-0.4939201794972253</v>
+        <v>0.2596303376760721</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>-1.045146571927231</v>
+        <v>0.1817907404268067</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>-1.269888849123424</v>
+        <v>0.121139499011627</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>-0.9066484084382448</v>
+        <v>0.06477724066014541</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>-0.3832923268660576</v>
+        <v>0.4430608569160513</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>-0.4939201794972253</v>
+        <v>0.2596303376760721</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>-1.045146571927231</v>
+        <v>0.1817907404268067</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>-1.269888849123424</v>
+        <v>0.121139499011627</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>-0.9066484084382448</v>
+        <v>0.06477724066014541</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>-4268.946947119827</v>
+        <v>4934.623419114325</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>-6112.427045752526</v>
+        <v>3213.012069125232</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>-14166.09421391498</v>
+        <v>2464.022583315532</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>-18170.32752601683</v>
+        <v>1733.33624820649</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>-14211.72322727036</v>
+        <v>1015.383920735108</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>-0.3652490570727081</v>
+        <v>0.42220401732948</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>-0.4713597638531824</v>
+        <v>0.247771400594907</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>-0.9981288326311496</v>
+        <v>0.1736125672696504</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>-1.221243887127643</v>
+        <v>0.1164990721509011</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>-0.8718015077939429</v>
+        <v>0.06228753677020595</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>-0.3652490570727081</v>
+        <v>0.42220401732948</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>-0.4713597638531824</v>
+        <v>0.247771400594907</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>-0.9981288326311496</v>
+        <v>0.1736125672696504</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>-1.221243887127643</v>
+        <v>0.1164990721509011</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>-0.8718015077939429</v>
+        <v>0.06228753677020595</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>-4268.946947119827</v>
+        <v>4934.623419114325</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>-6112.427045752526</v>
+        <v>3213.012069125232</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>-14166.09421391498</v>
+        <v>2464.022583315532</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>-18170.32752601683</v>
+        <v>1733.33624820649</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>-14211.72322727036</v>
+        <v>1015.383920735108</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>-0.230011633313067</v>
+        <v>0.3364685447422225</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>-0.230011633313067</v>
+        <v>0.3364685447422225</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>-18.22328930026536</v>
+        <v>26.65762397735412</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>-0.2360706840812028</v>
+        <v>0.3453319224988557</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>-0.2360706840812028</v>
+        <v>0.3453319224988557</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>-18.22328930026536</v>
+        <v>26.65762397735412</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>-0.3822096587343606</v>
+        <v>0.4423079630140244</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>-0.4904649987038933</v>
+        <v>0.2578141135302642</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>-1.037607460164104</v>
+        <v>0.1804794021452754</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>-1.26033300631413</v>
+        <v>0.1202279310335706</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>-0.8995079005648647</v>
+        <v>0.06426707333106317</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>-0.3822096587343606</v>
+        <v>0.4423079630140244</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>-0.4904649987038933</v>
+        <v>0.2578141135302642</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>-1.037607460164104</v>
+        <v>0.1804794021452754</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>-1.26033300631413</v>
+        <v>0.1202279310335706</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>-0.8995079005648647</v>
+        <v>0.06426707333106317</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>-4287.170236420092</v>
+        <v>4961.281043091679</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>-6112.427045752526</v>
+        <v>3213.012069125232</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>-14166.09421391498</v>
+        <v>2464.022583315532</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>-18170.32752601683</v>
+        <v>1733.33624820649</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>-14211.72322727036</v>
+        <v>1015.383920735108</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>-0.3644014708011495</v>
+        <v>0.4216996315663255</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>-0.4682922733279213</v>
+        <v>0.2461589667767496</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>-0.9914259054301934</v>
+        <v>0.1724466732872955</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>-1.212628872320814</v>
+        <v>0.1156772533134513</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>-0.8653655942695571</v>
+        <v>0.06182771054059268</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>-0.3644014708011495</v>
+        <v>0.4216996315663255</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>-0.4682922733279213</v>
+        <v>0.2461589667767496</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>-0.9914259054301934</v>
+        <v>0.1724466732872955</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>-1.212628872320814</v>
+        <v>0.1156772533134513</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>-0.8653655942695571</v>
+        <v>0.06182771054059268</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>-4287.170236420092</v>
+        <v>4961.281043091679</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>-6112.427045752526</v>
+        <v>3213.012069125232</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>-14166.09421391498</v>
+        <v>2464.022583315532</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>-18170.32752601683</v>
+        <v>1733.33624820649</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>-14211.72322727036</v>
+        <v>1015.383920735108</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>-0.3431657951877275</v>
+        <v>0.3971248773466075</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>-0.4393575457345483</v>
+        <v>0.2309493571931129</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>-0.9268918469349655</v>
+        <v>0.1612217459979476</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>-1.117670181663188</v>
+        <v>0.106618784754565</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>-0.7944551694744217</v>
+        <v>0.05676137875252945</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>-0.3431657951877275</v>
+        <v>0.3971248773466075</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>-0.4393575457345483</v>
+        <v>0.2309493571931129</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>-0.9268918469349655</v>
+        <v>0.1612217459979476</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>-1.117670181663188</v>
+        <v>0.106618784754565</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>-0.7944551694744217</v>
+        <v>0.05676137875252945</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>-4287.170236420092</v>
+        <v>4961.281043091679</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>-6112.427045752526</v>
+        <v>3213.012069125232</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>-14166.09421391498</v>
+        <v>2464.022583315532</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>-18170.32752601683</v>
+        <v>1733.33624820649</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>-14211.72322727036</v>
+        <v>1015.383920735108</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>-0.30266438975847</v>
+        <v>0.3502550672168992</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>-0.3873868702146486</v>
+        <v>0.2036308458332001</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>-0.8162455774883262</v>
+        <v>0.1419761513718486</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>-0.9851250830439398</v>
+        <v>0.09397480661878897</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>-0.6983170333725139</v>
+        <v>0.04989260457178783</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>-0.30266438975847</v>
+        <v>0.3502550672168992</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>-0.3873868702146486</v>
+        <v>0.2036308458332001</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>-0.8162455774883262</v>
+        <v>0.1419761513718486</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>-0.9851250830439398</v>
+        <v>0.09397480661878897</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>-0.6983170333725139</v>
+        <v>0.04989260457178783</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>-4287.170236420092</v>
+        <v>4961.281043091679</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>-6112.427045752526</v>
+        <v>3213.012069125232</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>-14166.09421391498</v>
+        <v>2464.022583315532</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>-18170.32752601683</v>
+        <v>1733.33624820649</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>-14211.72322727036</v>
+        <v>1015.383920735108</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>-2.06532742422631</v>
+        <v>2.396570227580816</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>-5.549086732877868</v>
+        <v>2.918868499467646</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>-19.10647003066494</v>
+        <v>3.300842687237557</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>-17.00263369738222</v>
+        <v>1.621429377899114</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>-22.87231061222449</v>
+        <v>1.631545107667912</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>-2.06532742422631</v>
+        <v>2.396570227580816</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>-5.549086732877868</v>
+        <v>2.918868499467646</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>-19.10647003066494</v>
+        <v>3.300842687237557</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>-17.00263369738222</v>
+        <v>1.621429377899114</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>-22.87231061222449</v>
+        <v>1.631545107667912</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>-28568.85691379299</v>
+        <v>33150.80752450721</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>-84743.26936573413</v>
+        <v>44575.70612980128</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>-318568.2197096255</v>
+        <v>55035.99444204655</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>-290127.2417122725</v>
+        <v>27667.52736157243</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>-427813.291931841</v>
+        <v>30517.10407752348</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>-2.060046897870849</v>
+        <v>2.39044279611353</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>-5.53489910412807</v>
+        <v>2.911405681776482</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>-19.05761955912553</v>
+        <v>3.292403256956077</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>-16.95916220986014</v>
+        <v>1.617283787973235</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>-22.81383182693291</v>
+        <v>1.627373654347676</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>-2.060046897870849</v>
+        <v>2.39044279611353</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>-5.53489910412807</v>
+        <v>2.911405681776482</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>-19.05761955912553</v>
+        <v>3.292403256956077</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>-16.95916220986014</v>
+        <v>1.617283787973235</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>-22.81383182693291</v>
+        <v>1.627373654347676</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>-28568.85691379299</v>
+        <v>33150.80752450721</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>-84743.26936573413</v>
+        <v>44575.70612980128</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>-318568.2197096255</v>
+        <v>55035.99444204655</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>-290127.2417122725</v>
+        <v>27667.52736157243</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>-427813.291931841</v>
+        <v>30517.10407752348</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>9.514797411060748</v>
+        <v>-10.80021536716234</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>26.75405245972444</v>
+        <v>-13.99862986578987</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>91.66223500497101</v>
+        <v>-16.71332180199745</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>40.12413317715507</v>
+        <v>-3.835925854965538</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>56.76691765479582</v>
+        <v>-4.10086569231246</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>9.514797411060748</v>
+        <v>-10.80021536716234</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>26.75405245972444</v>
+        <v>-13.99862986578987</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>91.66223500497101</v>
+        <v>-16.71332180199745</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>40.12413317715507</v>
+        <v>-3.835925854965538</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>56.76691765479582</v>
+        <v>-4.10086569231246</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>-25642.65960754503</v>
+        <v>29106.89890531744</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>-77486.07165318048</v>
+        <v>40543.34716057867</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>-285907.9369173802</v>
+        <v>52131.29873154636</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>-110544.7142621987</v>
+        <v>10568.23646995511</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>-171970.2154605428</v>
+        <v>12423.19974056477</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>11.76111530031779</v>
+        <v>-13.35000344345738</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>33.07033057412104</v>
+        <v>-17.30352132423093</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>113.3024769739269</v>
+        <v>-20.65911614009794</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>49.59691060508008</v>
+        <v>-4.741537240853374</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>70.16883649099869</v>
+        <v>-5.069025871463872</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>11.76111530031779</v>
+        <v>-13.35000344345738</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>33.07033057412104</v>
+        <v>-17.30352132423093</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>113.3024769739269</v>
+        <v>-20.65911614009794</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>49.59691060508008</v>
+        <v>-4.741537240853374</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>70.16883649099869</v>
+        <v>-5.069025871463872</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>-25642.65960754503</v>
+        <v>29106.89890531744</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>-77486.07165318048</v>
+        <v>40543.34716057867</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>-285907.9369173802</v>
+        <v>52131.29873154636</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>-110544.7142621987</v>
+        <v>10568.23646995511</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>-171970.2154605428</v>
+        <v>12423.19974056477</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>-4.867443556406916</v>
+        <v>5.589880000483783</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>-13.10908819622794</v>
+        <v>6.878121859799203</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>-44.59706206739015</v>
+        <v>7.906592134131158</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>-28.00218368765915</v>
+        <v>2.67222316481917</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>-38.2636752551829</v>
+        <v>2.739411504990448</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>-4.867443556406916</v>
+        <v>5.589880000483783</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>-13.10908819622794</v>
+        <v>6.878121859799203</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>-44.59706206739015</v>
+        <v>7.906592134131158</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>-28.00218368765915</v>
+        <v>2.67222316481917</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>-38.2636752551829</v>
+        <v>2.739411504990448</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>-54211.51652133802</v>
+        <v>62257.70642982466</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>-162229.3410189146</v>
+        <v>85119.05329037995</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>-604476.1566270057</v>
+        <v>107167.2931735929</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>-400671.9559744712</v>
+        <v>38235.76383152754</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>-599783.5073923838</v>
+        <v>42940.30381808826</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>-4.638311400252793</v>
+        <v>5.326739556776378</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>-12.51031436454856</v>
+        <v>6.563955129123403</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>-42.59078553740148</v>
+        <v>7.550900312841896</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>-26.92951881448906</v>
+        <v>2.569859722233934</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>-36.79301642261517</v>
+        <v>2.634122619409438</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>-4.638311400252793</v>
+        <v>5.326739556776378</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>-12.51031436454856</v>
+        <v>6.563955129123403</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>-42.59078553740148</v>
+        <v>7.550900312841896</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>-26.92951881448906</v>
+        <v>2.569859722233934</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>-36.79301642261517</v>
+        <v>2.634122619409438</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>-54211.51652133802</v>
+        <v>62257.70642982466</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>-162229.3410189146</v>
+        <v>85119.05329037995</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>-604476.1566270057</v>
+        <v>107167.2931735929</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>-400671.9559744712</v>
+        <v>38235.76383152754</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>-599783.5073923838</v>
+        <v>42940.30381808826</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>-4.720484108587774</v>
+        <v>6.905278640117741</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>-17.90944235120142</v>
+        <v>7.160283448354395</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>-150.3599730295389</v>
+        <v>6.767587659319601</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>-283.0865871559676</v>
+        <v>4.093305746233129</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>-455.3077081374828</v>
+        <v>2.308355626420994</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>-4.720484108587774</v>
+        <v>6.905278640117741</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>-17.90944235120142</v>
+        <v>7.160283448354395</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>-150.3599730295389</v>
+        <v>6.767587659319601</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>-283.0865871559676</v>
+        <v>4.093305746233129</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>-455.3077081374828</v>
+        <v>2.308355626420994</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>-373.9930294352345</v>
+        <v>547.0892430320381</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>-1561.35528967521</v>
+        <v>624.2375512553028</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>-14807.85866199513</v>
+        <v>666.4904197753459</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>-30711.42908792403</v>
+        <v>444.0735621690532</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>-56654.83257216455</v>
+        <v>287.2332253430812</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>-4.844832831529027</v>
+        <v>7.087180021565043</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>-18.38121944730696</v>
+        <v>7.348902259946292</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>-154.3208105617933</v>
+        <v>6.945861934472526</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>-290.5437578157739</v>
+        <v>4.201133106826545</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>-467.3015907032994</v>
+        <v>2.369163176586772</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>-4.844832831529027</v>
+        <v>7.087180021565043</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>-18.38121944730696</v>
+        <v>7.348902259946292</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>-154.3208105617933</v>
+        <v>6.945861934472526</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>-290.5437578157739</v>
+        <v>4.201133106826545</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>-467.3015907032994</v>
+        <v>2.369163176586772</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>-373.9930294352345</v>
+        <v>547.0892430320381</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>-1561.35528967521</v>
+        <v>624.2375512553028</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>-14807.85866199513</v>
+        <v>666.4904197753459</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>-30711.42908792403</v>
+        <v>444.0735621690532</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>-56654.83257216455</v>
+        <v>287.2332253430812</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>-4.866405537155322</v>
+        <v>5.599171060920672</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>-13.14266870612802</v>
+        <v>6.880095699585186</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>-45.359977458929</v>
+        <v>7.89837598314817</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>-29.9216796060053</v>
+        <v>2.682916732036798</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>-41.54819676608686</v>
+        <v>2.736016630123691</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>-4.866405537155322</v>
+        <v>5.599171060920672</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>-13.14266870612802</v>
+        <v>6.880095699585186</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>-45.359977458929</v>
+        <v>7.89837598314817</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>-29.9216796060053</v>
+        <v>2.682916732036798</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>-41.54819676608686</v>
+        <v>2.736016630123691</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>-54585.50955077325</v>
+        <v>62804.79567285669</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>-163790.6963085898</v>
+        <v>85743.29084163524</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>-619284.0152890009</v>
+        <v>107833.7835933683</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>-431383.3850623952</v>
+        <v>38679.83739369659</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>-656438.3399645484</v>
+        <v>43227.53704343134</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>-4.639666462449959</v>
+        <v>5.338290446722555</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>-12.54852073492022</v>
+        <v>6.569063367185445</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>-43.34110773972213</v>
+        <v>7.546837181839756</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>-28.78913145715979</v>
+        <v>2.58136720612833</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>-39.97116641525321</v>
+        <v>2.632166605286691</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>-4.639666462449959</v>
+        <v>5.338290446722555</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>-12.54852073492022</v>
+        <v>6.569063367185445</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>-43.34110773972213</v>
+        <v>7.546837181839756</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>-28.78913145715979</v>
+        <v>2.58136720612833</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>-39.97116641525321</v>
+        <v>2.632166605286691</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>-54585.50955077325</v>
+        <v>62804.79567285669</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>-163790.6963085898</v>
+        <v>85743.29084163524</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>-619284.0152890009</v>
+        <v>107833.7835933683</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>-431383.3850623952</v>
+        <v>38679.83739369659</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>-656438.3399645484</v>
+        <v>43227.53704343134</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>21.05476957722399</v>
+        <v>21.12226607932367</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>26.25252631264335</v>
+        <v>26.42536289539175</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>-20.55274818401081</v>
+        <v>33.23220957710473</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>-85.96821451499324</v>
+        <v>41.29933460223242</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>-180.1853499060198</v>
+        <v>50.41828845776774</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>21.05476957722399</v>
+        <v>21.12226607932367</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>26.25252631264335</v>
+        <v>26.42536289539175</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>-20.55274818401081</v>
+        <v>33.23220957710473</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>-85.96821451499324</v>
+        <v>41.29933460223242</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>-180.1853499060198</v>
+        <v>50.41828845776774</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>26870.04272529245</v>
+        <v>26956.18158749058</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>38057.73337007277</v>
+        <v>38308.29091659221</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>-33517.12424349409</v>
+        <v>54194.60635187374</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>-158202.1956510559</v>
+        <v>76000.71084250913</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>-376442.9675613057</v>
+        <v>105333.8139660262</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>11.19677584550791</v>
+        <v>11.23267000248712</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>13.96090569516086</v>
+        <v>14.05281895347696</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>-10.9298044598159</v>
+        <v>17.67265132591598</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>-45.71728150395795</v>
+        <v>21.96269070595992</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>-95.82128012099169</v>
+        <v>26.81208513373884</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>11.19677584550791</v>
+        <v>11.23267000248712</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>13.96090569516086</v>
+        <v>14.05281895347696</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>-10.9298044598159</v>
+        <v>17.67265132591598</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>-45.71728150395795</v>
+        <v>21.96269070595992</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>-95.82128012099169</v>
+        <v>26.81208513373884</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>26870.04272529245</v>
+        <v>26956.18158749058</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>38057.73337007277</v>
+        <v>38308.29091659221</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>-33517.12424349409</v>
+        <v>54194.60635187374</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>-158202.1956510559</v>
+        <v>76000.71084250913</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>-376442.9675613057</v>
+        <v>105333.8139660262</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>-2.218479716846317</v>
+        <v>7.184901797623951</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>-9.03760905465314</v>
+        <v>8.916752396031805</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>-42.7129768280218</v>
+        <v>10.60156676529254</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>-36.26584177739652</v>
+        <v>7.054084688174669</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>-57.73950710233631</v>
+        <v>8.304786928800659</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>-2.218479716846317</v>
+        <v>7.184901797623951</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>-9.03760905465314</v>
+        <v>8.916752396031805</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>-42.7129768280218</v>
+        <v>10.60156676529254</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>-36.26584177739652</v>
+        <v>7.054084688174669</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>-57.73950710233631</v>
+        <v>8.304786928800659</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>-27715.46682548081</v>
+        <v>89760.97726034728</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>-125732.962938517</v>
+        <v>124051.5817582275</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>-652801.1395324949</v>
+        <v>162028.389945242</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>-589585.5807134511</v>
+        <v>114680.5482362057</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>-1032881.307525854</v>
+        <v>148561.3510094575</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>-1.956648416324585</v>
+        <v>6.336919205082117</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>-7.968569380212533</v>
+        <v>7.862008600313682</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>-37.61418179750196</v>
+        <v>9.336021257747042</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>-31.96505639924314</v>
+        <v>6.217537050059011</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>-50.75236823591825</v>
+        <v>7.299812996053044</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>-1.956648416324585</v>
+        <v>6.336919205082117</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>-7.968569380212533</v>
+        <v>7.862008600313682</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>-37.61418179750196</v>
+        <v>9.336021257747042</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>-31.96505639924314</v>
+        <v>6.217537050059011</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>-50.75236823591825</v>
+        <v>7.299812996053044</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>-27715.46682548081</v>
+        <v>89760.97726034728</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>-125732.962938517</v>
+        <v>124051.5817582275</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>-652801.1395324949</v>
+        <v>162028.389945242</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>-589585.5807134511</v>
+        <v>114680.5482362057</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>-1032881.307525854</v>
+        <v>148561.3510094575</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>1066.803346774839</v>
+        <v>440.1244500856215</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>1453.994529960715</v>
+        <v>481.4666923984141</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>2715.28839943843</v>
+        <v>517.5328495361811</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>4466.945976043335</v>
+        <v>587.9504083543682</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>5663.327183568023</v>
+        <v>623.3799804796668</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>1066.803346774839</v>
+        <v>440.1244500856214</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>1453.994529960715</v>
+        <v>481.4666923984142</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>2715.28839943843</v>
+        <v>517.5328495361809</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>4466.945976043336</v>
+        <v>587.9504083543682</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>5663.327183568023</v>
+        <v>623.3799804796668</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>14756668.51254007</v>
+        <v>6088067.340445172</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>22204780.00077364</v>
+        <v>7352752.54625325</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>45272862.54441608</v>
+        <v>8628988.936908973</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>76222468.70534661</v>
+        <v>10032588.67276075</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>105929247.235493</v>
+        <v>11659960.64389209</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>1064.075797078525</v>
+        <v>438.9991617990776</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>1450.277029119884</v>
+        <v>480.2357023245577</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>2708.34608521371</v>
+        <v>516.2096473069672</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>4455.525110916465</v>
+        <v>586.4471660158406</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>5648.847470520282</v>
+        <v>621.7861535746556</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>1064.075797078525</v>
+        <v>438.9991617990776</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>1450.277029119884</v>
+        <v>480.2357023245577</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>2708.34608521371</v>
+        <v>516.2096473069672</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>4455.525110916465</v>
+        <v>586.4471660158406</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>5648.847470520282</v>
+        <v>621.7861535746556</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>14756668.51254007</v>
+        <v>6088067.340445172</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>22204780.00077364</v>
+        <v>7352752.54625325</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>45272862.54441608</v>
+        <v>8628988.936908973</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>76222468.70534661</v>
+        <v>10032588.67276075</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>105929247.235493</v>
+        <v>11659960.64389209</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>-2269.387344340672</v>
+        <v>-907.2236683407398</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>-3173.677683022603</v>
+        <v>-1013.222223497709</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>-5877.708871751102</v>
+        <v>-1096.702461340123</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>-11010.75247196285</v>
+        <v>-1403.705821024462</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>-13913.5287584767</v>
+        <v>-1493.313639219798</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>-2269.387344340672</v>
+        <v>-907.2236683407396</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>-3173.677683022603</v>
+        <v>-1013.22222349771</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>-5877.708871751102</v>
+        <v>-1096.702461340123</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>-11010.75247196285</v>
+        <v>-1403.705821024462</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>-13913.52875847669</v>
+        <v>-1493.313639219798</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>6116065.815647339</v>
+        <v>2444994.539571225</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>9191722.140822999</v>
+        <v>2934531.504291843</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>18333434.88986718</v>
+        <v>3420775.612955127</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>30335371.49452838</v>
+        <v>3867304.951068266</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>42149770.27574357</v>
+        <v>4523857.889351161</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>-2805.159696500261</v>
+        <v>-1121.40718352333</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>-3922.941030009067</v>
+        <v>-1252.430596320223</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>-7265.358236845404</v>
+        <v>-1355.619414762246</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>-13610.24557553634</v>
+        <v>-1735.102209281347</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>-17198.32897046294</v>
+        <v>-1845.865248794952</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>-2805.159696500261</v>
+        <v>-1121.40718352333</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>-3922.941030009067</v>
+        <v>-1252.430596320223</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>-7265.358236845404</v>
+        <v>-1355.619414762246</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>-13610.24557553634</v>
+        <v>-1735.102209281347</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>-17198.32897046294</v>
+        <v>-1845.865248794952</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>6116065.815647339</v>
+        <v>2444994.539571225</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>9191722.140822999</v>
+        <v>2934531.504291843</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>18333434.88986718</v>
+        <v>3420775.612955127</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>30335371.49452838</v>
+        <v>3867304.951068266</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>42149770.27574357</v>
+        <v>4523857.889351161</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>1874.082533189051</v>
+        <v>766.1508057602331</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>2537.022668293173</v>
+        <v>831.273264572537</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>4692.747535952816</v>
+        <v>889.0079313075724</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>7447.120194324872</v>
+        <v>971.4365297834372</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>9446.821008450501</v>
+        <v>1032.459827775341</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>1874.082533189051</v>
+        <v>766.1508057602331</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>2537.022668293173</v>
+        <v>831.273264572537</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>4692.747535952816</v>
+        <v>889.0079313075724</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>7447.120194324872</v>
+        <v>971.4365297834372</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>9446.821008450501</v>
+        <v>1032.459827775341</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>20872734.32818741</v>
+        <v>8533061.880016398</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>31396502.14159664</v>
+        <v>10287284.05054509</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>63606297.43428326</v>
+        <v>12049764.5498641</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>106557840.199875</v>
+        <v>13899893.62382902</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>148079017.5112365</v>
+        <v>16183818.53324326</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>1785.861156471665</v>
+        <v>730.0846893217612</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>2421.141017226972</v>
+        <v>793.3038291434623</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>4481.636112776162</v>
+        <v>849.0143607701012</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>7161.847291045961</v>
+        <v>934.2242232849205</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>9083.733807257448</v>
+        <v>992.7773833979281</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>1785.861156471665</v>
+        <v>730.0846893217612</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>2421.141017226972</v>
+        <v>793.3038291434623</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>4481.636112776162</v>
+        <v>849.0143607701012</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>7161.847291045961</v>
+        <v>934.2242232849205</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>9083.733807257448</v>
+        <v>992.7773833979281</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>20872734.32818741</v>
+        <v>8533061.880016398</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>31396502.14159664</v>
+        <v>10287284.05054509</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>63606297.43428326</v>
+        <v>12049764.5498641</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>106557840.199875</v>
+        <v>13899893.62382902</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>148079017.5112365</v>
+        <v>16183818.53324326</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1683.718306469329</v>
+        <v>1158.587663883502</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>2138.17163408273</v>
+        <v>1293.493074899624</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>5699.713059110317</v>
+        <v>1383.749824575836</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>9999.99098201629</v>
+        <v>1510.948708535558</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>13182.32785506114</v>
+        <v>1596.46031159991</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1683.71830646933</v>
+        <v>1158.587663883502</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>2138.171634082731</v>
+        <v>1293.493074899624</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>5699.713059110317</v>
+        <v>1383.749824575835</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>9999.99098201629</v>
+        <v>1510.948708535557</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>13182.32785506114</v>
+        <v>1596.46031159991</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>133397.1041246475</v>
+        <v>91792.21883064735</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>186407.0095339739</v>
+        <v>112767.4561300508</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>561323.2278024722</v>
+        <v>136275.4422804671</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>1084876.599098167</v>
+        <v>163919.437455064</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>1640302.951590611</v>
+        <v>198650.6928068248</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1728.071431357808</v>
+        <v>1189.107604869492</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>2194.49613513204</v>
+        <v>1327.566743679592</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>5849.856990056415</v>
+        <v>1420.201069744346</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>10263.41441051074</v>
+        <v>1550.750673337075</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>13529.58156812578</v>
+        <v>1638.514854398326</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1728.071431357808</v>
+        <v>1189.107604869492</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>2194.49613513204</v>
+        <v>1327.566743679592</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>5849.856990056415</v>
+        <v>1420.201069744346</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>10263.41441051074</v>
+        <v>1550.750673337075</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>13529.58156812578</v>
+        <v>1638.514854398326</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>133397.1041246475</v>
+        <v>91792.21883064735</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>186407.0095339739</v>
+        <v>112767.4561300508</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>561323.2278024722</v>
+        <v>136275.4422804671</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>1084876.599098167</v>
+        <v>163919.437455064</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>1640302.951590611</v>
+        <v>198650.6928068248</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>1872.737932790219</v>
+        <v>768.922706579213</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>2534.232536425698</v>
+        <v>834.5066878608209</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>4700.011230658049</v>
+        <v>892.5767268501659</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>7466.330404711754</v>
+        <v>975.4963288575166</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>9476.240809777055</v>
+        <v>1036.901736962913</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>1872.737932790219</v>
+        <v>768.922706579213</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>2534.232536425698</v>
+        <v>834.5066878608209</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>4700.011230658049</v>
+        <v>892.5767268501659</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>7466.330404711754</v>
+        <v>975.4963288575166</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>9476.240809777055</v>
+        <v>1036.901736962913</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>21006131.43231206</v>
+        <v>8624854.098847045</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>31582909.15113062</v>
+        <v>10400051.50667514</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>64167620.66208573</v>
+        <v>12186039.99214457</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>107642716.7989732</v>
+        <v>14063813.06128408</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>149719320.4628271</v>
+        <v>16382469.22605008</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>1785.481977074144</v>
+        <v>733.0965055611146</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>2419.666069465751</v>
+        <v>796.7806775170718</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>4490.824390516886</v>
+        <v>852.8501611229632</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>7183.726660875525</v>
+        <v>938.5733828197069</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>9116.554456769672</v>
+        <v>997.544420946797</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>1785.481977074144</v>
+        <v>733.0965055611146</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>2419.666069465751</v>
+        <v>796.7806775170718</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>4490.824390516886</v>
+        <v>852.8501611229632</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>7183.726660875525</v>
+        <v>938.5733828197069</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>9116.554456769672</v>
+        <v>997.544420946797</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>21006131.43231206</v>
+        <v>8624854.098847045</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>31582909.15113062</v>
+        <v>10400051.50667514</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>64167620.66208573</v>
+        <v>12186039.99214457</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>107642716.7989732</v>
+        <v>14063813.06128408</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>149719320.4628271</v>
+        <v>16382469.22605008</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>2492.610028446355</v>
+        <v>2478.251657674464</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>2646.82219841055</v>
+        <v>2616.717311279507</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>10412.58926083692</v>
+        <v>2757.471570709969</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>17930.53233980759</v>
+        <v>2917.397432310563</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>26017.0921982586</v>
+        <v>3089.0268566115</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2492.610028446355</v>
+        <v>2478.251657674464</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>2646.82219841055</v>
+        <v>2616.717311279507</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>10412.58926083692</v>
+        <v>2757.471570709969</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>17930.53233980759</v>
+        <v>2917.397432310563</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>26017.0921982586</v>
+        <v>3089.026856611501</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>3181062.500645834</v>
+        <v>3162738.384834866</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>3837042.28330153</v>
+        <v>3793399.863752079</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>16980699.84740293</v>
+        <v>4496844.723923089</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>32996492.96374653</v>
+        <v>5368713.099162824</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>54354870.69030221</v>
+        <v>6453590.357850485</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>1325.552182198646</v>
+        <v>1317.916503335009</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>1407.561111026169</v>
+        <v>1391.551547405714</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>5537.340482274971</v>
+        <v>1466.403655682795</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>9535.328831935205</v>
+        <v>1551.451084849562</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>13835.70351731307</v>
+        <v>1642.722384938733</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>1325.552182198646</v>
+        <v>1317.916503335009</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>1407.561111026169</v>
+        <v>1391.551547405714</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>5537.340482274971</v>
+        <v>1466.403655682795</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>9535.328831935205</v>
+        <v>1551.451084849562</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>13835.70351731307</v>
+        <v>1642.722384938733</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>3181062.500645834</v>
+        <v>3162738.384834866</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>3837042.28330153</v>
+        <v>3793399.863752079</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>16980699.84740293</v>
+        <v>4496844.723923089</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>32996492.96374653</v>
+        <v>5368713.099162824</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>54354870.69030221</v>
+        <v>6453590.357850485</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>1936.05972742855</v>
+        <v>943.535788163466</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>2545.964608785461</v>
+        <v>1020.21666891663</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>5309.559257260062</v>
+        <v>1091.566213889071</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>8650.821010210144</v>
+        <v>1195.308946017797</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>11408.03219463308</v>
+        <v>1276.567612296534</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>1936.05972742855</v>
+        <v>943.535788163466</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>2545.964608785461</v>
+        <v>1020.21666891663</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>5309.559257260062</v>
+        <v>1091.566213889071</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>8650.821010210144</v>
+        <v>1195.308946017797</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>11408.03219463308</v>
+        <v>1276.567612296534</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>24187193.93295789</v>
+        <v>11787592.48368191</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>35419951.43443215</v>
+        <v>14193451.37042722</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>81148320.50948867</v>
+        <v>16682884.71606766</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>140639209.7627197</v>
+        <v>19432526.16044691</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>204074191.1531293</v>
+        <v>22836059.58390056</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>1707.560439167766</v>
+        <v>832.1770046561601</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>2244.807836009149</v>
+        <v>899.5373953386282</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>4675.738897134578</v>
+        <v>961.2621985714213</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>7624.915566236061</v>
+        <v>1053.556625226133</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>10027.53019285475</v>
+        <v>1122.088372221298</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>1707.560439167766</v>
+        <v>832.1770046561601</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>2244.807836009149</v>
+        <v>899.5373953386282</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>4675.738897134578</v>
+        <v>961.2621985714213</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>7624.915566236061</v>
+        <v>1053.556625226133</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>10027.53019285475</v>
+        <v>1122.088372221298</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>24187193.93295789</v>
+        <v>11787592.48368191</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>35419951.43443215</v>
+        <v>14193451.37042722</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>81148320.50948867</v>
+        <v>16682884.71606766</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>140639209.7627197</v>
+        <v>19432526.16044691</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>204074191.1531293</v>
+        <v>22836059.58390056</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9404,19 +9404,19 @@
         </is>
       </c>
       <c r="C91" s="79" t="n">
-        <v>-2695.029489302209</v>
+        <v>-2695.029489302215</v>
       </c>
       <c r="D91" s="80" t="n">
-        <v>-2896.236813837008</v>
+        <v>-2896.236813836996</v>
       </c>
       <c r="E91" s="80" t="n">
-        <v>-3119.146471847156</v>
+        <v>-3119.146471847148</v>
       </c>
       <c r="F91" s="80" t="n">
-        <v>-2755.067973035689</v>
+        <v>-2755.067973035692</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>-3029.40907424827</v>
+        <v>-3029.409074248268</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>0</v>
@@ -9434,19 +9434,19 @@
         <v>0</v>
       </c>
       <c r="M91" s="79" t="n">
-        <v>-2695.029489302209</v>
+        <v>-2695.029489302215</v>
       </c>
       <c r="N91" s="80" t="n">
-        <v>-2896.236813837008</v>
+        <v>-2896.236813836996</v>
       </c>
       <c r="O91" s="80" t="n">
-        <v>-3119.146471847156</v>
+        <v>-3119.146471847148</v>
       </c>
       <c r="P91" s="80" t="n">
-        <v>-2755.067973035689</v>
+        <v>-2755.067973035692</v>
       </c>
       <c r="Q91" s="81" t="n">
-        <v>-3029.40907424827</v>
+        <v>-3029.409074248268</v>
       </c>
       <c r="S91" s="32" t="inlineStr">
         <is>
@@ -9454,19 +9454,19 @@
         </is>
       </c>
       <c r="T91" s="79" t="n">
-        <v>-2180.291490455174</v>
+        <v>-2180.291490455178</v>
       </c>
       <c r="U91" s="80" t="n">
-        <v>-2343.069159212356</v>
+        <v>-2343.069159212347</v>
       </c>
       <c r="V91" s="80" t="n">
-        <v>-2523.404117486091</v>
+        <v>-2523.404117486085</v>
       </c>
       <c r="W91" s="80" t="n">
-        <v>-2228.862905240631</v>
+        <v>-2228.862905240634</v>
       </c>
       <c r="X91" s="81" t="n">
-        <v>-2450.8061421626</v>
+        <v>-2450.806142162598</v>
       </c>
       <c r="Y91" s="79" t="n">
         <v>0</v>
@@ -9484,19 +9484,19 @@
         <v>0</v>
       </c>
       <c r="AD91" s="79" t="n">
-        <v>-2180.291490455174</v>
+        <v>-2180.291490455178</v>
       </c>
       <c r="AE91" s="80" t="n">
-        <v>-2343.069159212356</v>
+        <v>-2343.069159212347</v>
       </c>
       <c r="AF91" s="80" t="n">
-        <v>-2523.404117486091</v>
+        <v>-2523.404117486085</v>
       </c>
       <c r="AG91" s="80" t="n">
-        <v>-2228.862905240631</v>
+        <v>-2228.862905240634</v>
       </c>
       <c r="AH91" s="81" t="n">
-        <v>-2450.8061421626</v>
+        <v>-2450.806142162598</v>
       </c>
       <c r="AJ91" s="120" t="n">
         <v>72.8104218970057</v>
@@ -9524,13 +9524,13 @@
         </is>
       </c>
       <c r="C92" s="85" t="n">
-        <v>11137.57476447375</v>
+        <v>11137.57476447374</v>
       </c>
       <c r="D92" s="86" t="n">
-        <v>12375.33370670243</v>
+        <v>12375.33370670244</v>
       </c>
       <c r="E92" s="86" t="n">
-        <v>13554.16990728197</v>
+        <v>13554.16990728198</v>
       </c>
       <c r="F92" s="86" t="n">
         <v>14308.59680243621</v>
@@ -9554,13 +9554,13 @@
         <v>0</v>
       </c>
       <c r="M92" s="85" t="n">
-        <v>11137.57476447375</v>
+        <v>11137.57476447374</v>
       </c>
       <c r="N92" s="86" t="n">
-        <v>12375.33370670243</v>
+        <v>12375.33370670244</v>
       </c>
       <c r="O92" s="86" t="n">
-        <v>13554.16990728197</v>
+        <v>13554.16990728198</v>
       </c>
       <c r="P92" s="86" t="n">
         <v>14308.59680243621</v>
@@ -9577,10 +9577,10 @@
         <v>11687.7699324766</v>
       </c>
       <c r="U92" s="86" t="n">
-        <v>12967.64703840187</v>
+        <v>12967.64703840188</v>
       </c>
       <c r="V92" s="86" t="n">
-        <v>14192.65103941742</v>
+        <v>14192.65103941743</v>
       </c>
       <c r="W92" s="86" t="n">
         <v>14878.54122959282</v>
@@ -9607,10 +9607,10 @@
         <v>11687.7699324766</v>
       </c>
       <c r="AE92" s="86" t="n">
-        <v>12967.64703840187</v>
+        <v>12967.64703840188</v>
       </c>
       <c r="AF92" s="86" t="n">
-        <v>14192.65103941742</v>
+        <v>14192.65103941743</v>
       </c>
       <c r="AG92" s="86" t="n">
         <v>14878.54122959282</v>
@@ -9759,10 +9759,10 @@
         <v>11216.80244977722</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>12462.51427095771</v>
+        <v>12462.51427095772</v>
       </c>
       <c r="E94" s="86" t="n">
-        <v>13652.65262421546</v>
+        <v>13652.65262421547</v>
       </c>
       <c r="F94" s="86" t="n">
         <v>14417.08456018011</v>
@@ -9789,10 +9789,10 @@
         <v>11216.80244977722</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>12462.51427095771</v>
+        <v>12462.51427095772</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>13652.65262421546</v>
+        <v>13652.65262421547</v>
       </c>
       <c r="P94" s="86" t="n">
         <v>14417.08456018011</v>
@@ -9809,7 +9809,7 @@
         <v>11764.96413967429</v>
       </c>
       <c r="U94" s="86" t="n">
-        <v>13052.59000391899</v>
+        <v>13052.590003919</v>
       </c>
       <c r="V94" s="86" t="n">
         <v>14288.60607366127</v>
@@ -9839,7 +9839,7 @@
         <v>11764.96413967429</v>
       </c>
       <c r="AE94" s="86" t="n">
-        <v>13052.59000391899</v>
+        <v>13052.590003919</v>
       </c>
       <c r="AF94" s="86" t="n">
         <v>14288.60607366127</v>
@@ -9991,7 +9991,7 @@
         <v>12492.99987510355</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>13912.1931672605</v>
+        <v>13912.19316726051</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>15283.4381495093</v>
@@ -10021,7 +10021,7 @@
         <v>12492.99987510355</v>
       </c>
       <c r="N96" s="133" t="n">
-        <v>13912.1931672605</v>
+        <v>13912.19316726051</v>
       </c>
       <c r="O96" s="133" t="n">
         <v>15283.4381495093</v>
@@ -10038,13 +10038,13 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>14164.76593047933</v>
+        <v>14164.76593047932</v>
       </c>
       <c r="U96" s="136" t="n">
         <v>15778.6118108899</v>
       </c>
       <c r="V96" s="136" t="n">
-        <v>17355.18648383438</v>
+        <v>17355.18648383439</v>
       </c>
       <c r="W96" s="136" t="n">
         <v>18444.69076949325</v>
@@ -10068,13 +10068,13 @@
         <v>0</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>14164.76593047933</v>
+        <v>14164.76593047932</v>
       </c>
       <c r="AE96" s="136" t="n">
         <v>15778.6118108899</v>
       </c>
       <c r="AF96" s="136" t="n">
-        <v>17355.18648383438</v>
+        <v>17355.18648383439</v>
       </c>
       <c r="AG96" s="136" t="n">
         <v>18444.69076949325</v>
